--- a/data/satisfaction_detail/2026/6月/会议主承办.xlsx
+++ b/data/satisfaction_detail/2026/6月/会议主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="4">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="15">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="18">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="21">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>10</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>10</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="29">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.83</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.92</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.67</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="31">
